--- a/excel_config/yunxing_params/境界突破.xlsx
+++ b/excel_config/yunxing_params/境界突破.xlsx
@@ -1193,7 +1193,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>json</t>
+          <t>string</t>
         </is>
       </c>
     </row>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>[{"min_total":2400,"quality":1,"label":"一品筑基","success_rate":1,"foundation_growth":2,"perks":["all_stats_percent_2","next_breakthrough_discount_3"]},{"min_total":2100,"quality":2,"label":"极品筑基","success_rate":0.97,"foundation_growth":1.8,"perks":["hp_mp_cap_percent_3"]},{"min_total":1800,"quality":3,"label":"上品筑基","success_rate":0.92,"foundation_growth":1.5,"perks":["unlock_premium_foundation_passive"]},{"min_total":1500,"quality":4,"label":"中品筑基","success_rate":0.8,"foundation_growth":1.2,"perks":[]},{"min_total":1200,"quality":5,"label":"下品筑基","success_rate":0.65,"foundation_growth":1,"perks":["cultivation_speed_penalty_5"]}]</t>
+          <t>[{"min_total": 2400, "quality": 1, "label": "一品筑基", "success_rate": 1, "foundation_growth": 2, "perks": ["all_stats_percent_2", "next_breakthrough_discount_3"]}, {"min_total": 2100, "quality": 2, "label": "极品筑基", "success_rate": 0.97, "foundation_growth": 1.8, "perks": ["hp_mp_cap_percent_3"]}, {"min_total": 1800, "quality": 3, "label": "上品筑基", "success_rate": 0.92, "foundation_growth": 1.5, "perks": ["unlock_premium_foundation_passive"]}, {"min_total": 1500, "quality": 4, "label": "中品筑基", "success_rate": 0.8, "foundation_growth": 1.2, "perks": []}, {"min_total": 1200, "quality": 5, "label": "下品筑基", "success_rate": 0.65, "foundation_growth": 1, "perks": ["cultivation_speed_penalty_5"]}]</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>[{"min_total":3600,"quality":1,"label":"一品金丹","success_rate":1,"foundation_growth":2.5,"perks":["core_passive_tier_1"]},{"min_total":3150,"quality":2,"label":"极品金丹","success_rate":0.97,"foundation_growth":2.2,"perks":["core_passive_tier_2"]},{"min_total":2700,"quality":3,"label":"上品金丹","success_rate":0.92,"foundation_growth":1.9,"perks":["core_passive_tier_3"]},{"min_total":2250,"quality":4,"label":"中品金丹","success_rate":0.8,"foundation_growth":1.6,"perks":[]},{"min_total":1800,"quality":5,"label":"下品金丹","success_rate":0.65,"foundation_growth":1.3,"perks":["cultivation_speed_penalty_5"]}]</t>
+          <t>[{"min_total": 3600, "quality": 1, "label": "一品金丹", "success_rate": 1, "foundation_growth": 2.5, "perks": ["core_passive_tier_1"]}, {"min_total": 3150, "quality": 2, "label": "极品金丹", "success_rate": 0.97, "foundation_growth": 2.2, "perks": ["core_passive_tier_2"]}, {"min_total": 2700, "quality": 3, "label": "上品金丹", "success_rate": 0.92, "foundation_growth": 1.9, "perks": ["core_passive_tier_3"]}, {"min_total": 2250, "quality": 4, "label": "中品金丹", "success_rate": 0.8, "foundation_growth": 1.6, "perks": []}, {"min_total": 1800, "quality": 5, "label": "下品金丹", "success_rate": 0.65, "foundation_growth": 1.3, "perks": ["cultivation_speed_penalty_5"]}]</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>[{"min_total":4800,"quality":1,"label":"一品元婴","success_rate":1,"foundation_growth":3,"perks":["nascent_avatar_tier_1"]},{"min_total":4200,"quality":2,"label":"极品元婴","success_rate":0.97,"foundation_growth":2.6,"perks":["nascent_avatar_tier_2"]},{"min_total":3600,"quality":3,"label":"上品元婴","success_rate":0.92,"foundation_growth":2.2,"perks":["nascent_avatar_tier_3"]},{"min_total":3000,"quality":4,"label":"中品元婴","success_rate":0.8,"foundation_growth":1.9,"perks":[]},{"min_total":2400,"quality":5,"label":"下品元婴","success_rate":0.65,"foundation_growth":1.5,"perks":["cultivation_speed_penalty_5"]}]</t>
+          <t>[{"min_total": 4800, "quality": 1, "label": "一品元婴", "success_rate": 1, "foundation_growth": 3, "perks": ["nascent_avatar_tier_1"]}, {"min_total": 4200, "quality": 2, "label": "极品元婴", "success_rate": 0.97, "foundation_growth": 2.6, "perks": ["nascent_avatar_tier_2"]}, {"min_total": 3600, "quality": 3, "label": "上品元婴", "success_rate": 0.92, "foundation_growth": 2.2, "perks": ["nascent_avatar_tier_3"]}, {"min_total": 3000, "quality": 4, "label": "中品元婴", "success_rate": 0.8, "foundation_growth": 1.9, "perks": []}, {"min_total": 2400, "quality": 5, "label": "下品元婴", "success_rate": 0.65, "foundation_growth": 1.5, "perks": ["cultivation_speed_penalty_5"]}]</t>
         </is>
       </c>
     </row>
